--- a/tests/TC-12/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-12/results/timetable_all_departments_even.xlsx
@@ -837,8 +837,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>CS999
 LEC
@@ -846,9 +845,10 @@
 Dr. Test</t>
         </is>
       </c>
+      <c r="G3" s="11" t="n"/>
       <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
@@ -896,17 +896,17 @@
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>CS999
-TUT
+LEC
 Room: 101
 Dr. Test</t>
         </is>
       </c>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="12" t="n"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
@@ -940,15 +940,8 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>CS999
-LEC
-Room: 101
-Dr. Test</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr"/>
@@ -993,7 +986,14 @@
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>CS999
+TUT
+Room: 101
+Dr. Test</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1068,10 +1068,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G3:J3"/>
+  <mergeCells count="2">
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="F3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1270,8 +1269,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>CS999
 LEC
@@ -1279,9 +1277,10 @@
 Dr. Test</t>
         </is>
       </c>
+      <c r="G3" s="11" t="n"/>
       <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
@@ -1329,17 +1328,17 @@
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>CS999
-TUT
+LEC
 Room: 101
 Dr. Test</t>
         </is>
       </c>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="12" t="n"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
@@ -1373,15 +1372,8 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>CS999
-LEC
-Room: 101
-Dr. Test</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr"/>
@@ -1426,7 +1418,14 @@
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>CS999
+TUT
+Room: 101
+Dr. Test</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1501,10 +1500,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G3:J3"/>
+  <mergeCells count="2">
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="F3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1516,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,10 +1569,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1607,10 +1605,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1624,7 +1622,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1636,17 +1634,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1676,13 +1674,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1700,78 +1698,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>CS999</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Dr. Test</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CS999</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Dr. Test</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>CS999</t>
         </is>

--- a/tests/TC-12/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-12/results/timetable_all_departments_even.xlsx
@@ -837,17 +837,10 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CS999
-LEC
-Room: 101
-Dr. Test</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
@@ -897,18 +890,18 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr">
         <is>
           <t>CS999
-LEC
+TUT
 Room: 101
 Dr. Test</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -941,9 +934,16 @@
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>CS999
+LEC
+Room: 101
+Dr. Test</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="n"/>
+      <c r="P5" s="12" t="n"/>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="8" t="inlineStr"/>
@@ -983,17 +983,17 @@
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>CS999
-TUT
+LEC
 Room: 101
 Dr. Test</t>
         </is>
       </c>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1069,8 +1069,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1269,17 +1269,10 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CS999
-LEC
-Room: 101
-Dr. Test</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
@@ -1329,18 +1322,18 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr">
         <is>
           <t>CS999
-LEC
+TUT
 Room: 101
 Dr. Test</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1373,9 +1366,16 @@
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>CS999
+LEC
+Room: 101
+Dr. Test</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="n"/>
+      <c r="P5" s="12" t="n"/>
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="8" t="inlineStr"/>
@@ -1415,17 +1415,17 @@
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>CS999
-TUT
+LEC
 Room: 101
 Dr. Test</t>
         </is>
       </c>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1501,8 +1501,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1674,13 +1674,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
